--- a/app/data/sources.xlsx
+++ b/app/data/sources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Артём\Documents\coding\HSE_учеба\AI_FINAL_PROJ_TG\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03205775-BB1A-4D7D-88B9-6B8453FB7C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCCD602-FA44-45FC-B97C-198D10FE705B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="232">
   <si>
     <t>source_id</t>
   </si>
@@ -691,13 +691,52 @@
   </si>
   <si>
     <t>https://stopgame.ru/rss/rss_news.xml</t>
+  </si>
+  <si>
+    <t>https://www.retail.ru/rss/news/</t>
+  </si>
+  <si>
+    <t>E-commerce</t>
+  </si>
+  <si>
+    <t>retail_ru_ecommerce</t>
+  </si>
+  <si>
+    <t>Retail.ru</t>
+  </si>
+  <si>
+    <t>Ритейл, онлайн-торговля, маркетплейсы, сети, бренды</t>
+  </si>
+  <si>
+    <t>https://oborot.ru/feed/</t>
+  </si>
+  <si>
+    <t>Oborot.ru</t>
+  </si>
+  <si>
+    <t>oborot</t>
+  </si>
+  <si>
+    <t>Интернет-магазины, селлеры, маркетплейсы, логистика, реклама, ПВЗ</t>
+  </si>
+  <si>
+    <t>https://new-retail.ru/rss/</t>
+  </si>
+  <si>
+    <t>New Retail</t>
+  </si>
+  <si>
+    <t>new_retail</t>
+  </si>
+  <si>
+    <t>Ритейл, e-commerce, омниканальность, потребительский рынок</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -724,6 +763,13 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -743,7 +789,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -758,13 +804,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -783,12 +853,30 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -846,7 +934,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SourcesTable" displayName="SourcesTable" ref="A1:F51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SourcesTable" displayName="SourcesTable" ref="A1:F54">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="source_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="title"/>
@@ -860,7 +948,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="CategorySummaryTable" displayName="CategorySummaryTable" ref="A1:B13" totalsRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="CategorySummaryTable" displayName="CategorySummaryTable" ref="A1:B14" totalsRowCount="1">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B12">
     <sortCondition descending="1" ref="B2:B12"/>
   </sortState>
@@ -1023,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -2053,6 +2141,66 @@
         <v>1</v>
       </c>
     </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>221</v>
+      </c>
+      <c r="B52" t="s">
+        <v>222</v>
+      </c>
+      <c r="C52" t="s">
+        <v>220</v>
+      </c>
+      <c r="D52" t="s">
+        <v>223</v>
+      </c>
+      <c r="E52" t="s">
+        <v>219</v>
+      </c>
+      <c r="F52" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C53" t="s">
+        <v>220</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="F53" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F54" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -2064,7 +2212,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2179,12 +2327,21 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13">
+        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <f>SUBTOTAL(109,CategorySummaryTable[active_sources_count])</f>
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/app/data/sources.xlsx
+++ b/app/data/sources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Артём\Documents\coding\HSE_учеба\AI_FINAL_PROJ_TG\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCCD602-FA44-45FC-B97C-198D10FE705B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8204158D-256F-4E11-8123-1452A5DFBD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="228">
   <si>
     <t>source_id</t>
   </si>
@@ -450,12 +450,6 @@
     <t>http://pedsovet.org/rss/</t>
   </si>
   <si>
-    <t>portal_kultura</t>
-  </si>
-  <si>
-    <t>Газета «Культура»</t>
-  </si>
-  <si>
     <t>kino_teatr</t>
   </si>
   <si>
@@ -546,9 +540,6 @@
     <t>gazeta_ru_culture</t>
   </si>
   <si>
-    <t>https://portal-kultura.ru/rss/</t>
-  </si>
-  <si>
     <t>https://www.kino-teatr.ru/rss/rss.xml</t>
   </si>
   <si>
@@ -565,9 +556,6 @@
   </si>
   <si>
     <t>Новости культуры, кино, музыки, театра, литературы и событий культурной жизни</t>
-  </si>
-  <si>
-    <t>Новости культуры, искусства, театра, кино, литературы, музыки и культурной политики</t>
   </si>
   <si>
     <t>Новости кино, сериалов, театра, актеров, премьер, фестивалей и российской индустрии развлечений</t>
@@ -834,7 +822,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -859,7 +847,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -867,9 +855,8 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -934,7 +921,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SourcesTable" displayName="SourcesTable" ref="A1:F54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SourcesTable" displayName="SourcesTable" ref="A1:F53">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="source_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="title"/>
@@ -1111,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -1403,19 +1390,19 @@
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F15" s="3" t="b">
         <v>1</v>
@@ -1423,19 +1410,19 @@
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="F16" s="3" t="b">
         <v>1</v>
@@ -1443,19 +1430,19 @@
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F17" s="3" t="b">
         <v>1</v>
@@ -1463,19 +1450,19 @@
     </row>
     <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F18" s="3" t="b">
         <v>1</v>
@@ -1483,19 +1470,19 @@
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F19" s="3" t="b">
         <v>1</v>
@@ -1812,7 +1799,7 @@
         <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>132</v>
@@ -1832,10 +1819,10 @@
         <v>85</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F36" s="3" t="b">
         <v>1</v>
@@ -1852,7 +1839,7 @@
         <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>137</v>
@@ -1863,19 +1850,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F38" s="3" t="b">
         <v>1</v>
@@ -1891,51 +1878,51 @@
       <c r="C39" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" t="s">
+        <v>141</v>
+      </c>
+      <c r="C40" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" t="s">
+        <v>175</v>
+      </c>
+      <c r="E40" t="s">
+        <v>169</v>
+      </c>
+      <c r="F40" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41" t="s">
+        <v>188</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>177</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F39" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F40" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>142</v>
-      </c>
-      <c r="B41" t="s">
-        <v>143</v>
-      </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E41" t="s">
-        <v>172</v>
       </c>
       <c r="F41" s="3" t="b">
         <v>1</v>
@@ -1943,19 +1930,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>190</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>191</v>
       </c>
       <c r="C42" t="s">
         <v>94</v>
       </c>
       <c r="D42" t="s">
-        <v>192</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>181</v>
+        <v>191</v>
+      </c>
+      <c r="E42" t="s">
+        <v>178</v>
       </c>
       <c r="F42" s="3" t="b">
         <v>1</v>
@@ -1963,19 +1950,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>194</v>
       </c>
       <c r="C43" t="s">
         <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E43" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F43" s="3" t="b">
         <v>1</v>
@@ -1983,19 +1970,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="C44" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" t="s">
         <v>197</v>
       </c>
-      <c r="C44" t="s">
-        <v>94</v>
-      </c>
-      <c r="D44" t="s">
-        <v>198</v>
-      </c>
-      <c r="E44" t="s">
-        <v>183</v>
+      <c r="E44" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="F44" s="3" t="b">
         <v>1</v>
@@ -2003,19 +1990,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="C45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" t="s">
         <v>200</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D45" t="s">
-        <v>201</v>
-      </c>
       <c r="E45" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F45" s="3" t="b">
         <v>1</v>
@@ -2023,19 +2010,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>202</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>203</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>204</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="E46" t="s">
+        <v>182</v>
       </c>
       <c r="F46" s="3" t="b">
         <v>1</v>
@@ -2043,39 +2030,39 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" t="s">
         <v>205</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="E47" t="s">
+        <v>183</v>
+      </c>
+      <c r="F47" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>128</v>
+      </c>
+      <c r="C48" t="s">
+        <v>129</v>
+      </c>
+      <c r="D48" t="s">
         <v>206</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D47" t="s">
-        <v>207</v>
-      </c>
-      <c r="E47" t="s">
-        <v>186</v>
-      </c>
-      <c r="F47" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D48" t="s">
-        <v>209</v>
-      </c>
       <c r="E48" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F48" s="3" t="b">
         <v>1</v>
@@ -2083,19 +2070,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="D49" t="s">
+        <v>209</v>
+      </c>
+      <c r="E49" t="s">
         <v>210</v>
-      </c>
-      <c r="E49" t="s">
-        <v>189</v>
       </c>
       <c r="F49" s="3" t="b">
         <v>1</v>
@@ -2109,7 +2096,7 @@
         <v>212</v>
       </c>
       <c r="C50" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D50" t="s">
         <v>213</v>
@@ -2123,81 +2110,61 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" t="s">
+        <v>218</v>
+      </c>
+      <c r="C51" t="s">
+        <v>216</v>
+      </c>
+      <c r="D51" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" t="s">
         <v>215</v>
       </c>
-      <c r="B51" t="s">
+      <c r="F51" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C52" t="s">
         <v>216</v>
       </c>
-      <c r="C51" t="s">
-        <v>151</v>
-      </c>
-      <c r="D51" t="s">
-        <v>217</v>
-      </c>
-      <c r="E51" t="s">
-        <v>218</v>
-      </c>
-      <c r="F51" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>221</v>
-      </c>
-      <c r="B52" t="s">
-        <v>222</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="D52" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="D52" t="s">
-        <v>223</v>
-      </c>
-      <c r="E52" t="s">
-        <v>219</v>
-      </c>
-      <c r="F52" s="3" t="b">
+      <c r="F52" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C53" t="s">
-        <v>220</v>
-      </c>
-      <c r="D53" s="7" t="s">
+      <c r="C53" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="F53" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F54" s="12" t="b">
+      <c r="F53" s="11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2224,7 +2191,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2269,7 +2236,7 @@
       </c>
       <c r="B6">
         <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -2319,7 +2286,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B12">
         <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
@@ -2328,7 +2295,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B13">
         <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
@@ -2337,11 +2304,11 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B14">
         <f>SUBTOTAL(109,CategorySummaryTable[active_sources_count])</f>
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/app/data/sources.xlsx
+++ b/app/data/sources.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Артём\Documents\coding\HSE_учеба\AI_FINAL_PROJ_TG\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8204158D-256F-4E11-8123-1452A5DFBD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62006A5A-52F9-43F4-A57E-C5465C66B4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -870,7 +870,10 @@
     <cellStyle name="Гиперссылка" xfId="2" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -940,9 +943,9 @@
     <sortCondition descending="1" ref="B2:B12"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="category" totalsRowLabel="ВСЕГО" totalsRowDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="active_sources_count" totalsRowFunction="sum">
-      <calculatedColumnFormula>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="category" totalsRowLabel="ВСЕГО" totalsRowDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="active_sources_count" totalsRowFunction="sum" dataDxfId="0">
+      <calculatedColumnFormula>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1845,7 +1848,7 @@
         <v>137</v>
       </c>
       <c r="F37" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2025,7 +2028,7 @@
         <v>182</v>
       </c>
       <c r="F46" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2199,7 +2202,7 @@
         <v>34</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
         <v>9</v>
       </c>
     </row>
@@ -2208,7 +2211,7 @@
         <v>104</v>
       </c>
       <c r="B3">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
         <v>6</v>
       </c>
     </row>
@@ -2217,7 +2220,7 @@
         <v>85</v>
       </c>
       <c r="B4">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
         <v>5</v>
       </c>
     </row>
@@ -2226,7 +2229,7 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
         <v>4</v>
       </c>
     </row>
@@ -2235,7 +2238,7 @@
         <v>99</v>
       </c>
       <c r="B6">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
         <v>3</v>
       </c>
     </row>
@@ -2244,7 +2247,7 @@
         <v>61</v>
       </c>
       <c r="B7">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
         <v>4</v>
       </c>
     </row>
@@ -2253,7 +2256,7 @@
         <v>72</v>
       </c>
       <c r="B8">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
         <v>3</v>
       </c>
     </row>
@@ -2262,8 +2265,8 @@
         <v>94</v>
       </c>
       <c r="B9">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
-        <v>6</v>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -2271,8 +2274,8 @@
         <v>25</v>
       </c>
       <c r="B10">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
-        <v>4</v>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -2280,7 +2283,7 @@
         <v>129</v>
       </c>
       <c r="B11">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
         <v>2</v>
       </c>
     </row>
@@ -2289,7 +2292,7 @@
         <v>149</v>
       </c>
       <c r="B12">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
         <v>3</v>
       </c>
     </row>
@@ -2298,7 +2301,7 @@
         <v>216</v>
       </c>
       <c r="B13">
-        <f>COUNTIF(SourcesTable[category], CategorySummaryTable[[#This Row],[category]])</f>
+        <f>COUNTIFS(SourcesTable[category],CategorySummaryTable[[#This Row],[category]],SourcesTable[is_active],TRUE)</f>
         <v>3</v>
       </c>
     </row>
@@ -2308,7 +2311,7 @@
       </c>
       <c r="B14">
         <f>SUBTOTAL(109,CategorySummaryTable[active_sources_count])</f>
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
